--- a/testing/TEST_CASES.xlsx
+++ b/testing/TEST_CASES.xlsx
@@ -463,16 +463,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="57" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="49" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -857,17 +857,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TC-EVAL-001</t>
+          <t>TC-AUTH-009</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Execute correct Python code solution</t>
+          <t>Enforce legitimate email check during signup &amp; login</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -877,17 +877,17 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Challenge exists</t>
+          <t>Signup / Login page</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>POST /api/challenges/&lt;pk&gt;/run with valid code</t>
+          <t>Enter fake format e.g. bajnjnjdn@invalid or test@foo.bar</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200 + success: true</t>
+          <t>Rejected with friendly legitimacy error</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -899,37 +899,37 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC-EVAL-002</t>
+          <t>TC-AUTH-010</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Execute failing Python code solution</t>
+          <t>Mandatory Email OTP verification via live Gmail SMTP</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Challenge exists</t>
+          <t>Signup/Forgot Pwd</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>POST /api/challenges/&lt;pk&gt;/run with wrong code</t>
+          <t>Request 6-digit OTP to user email and verify code</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200 + success: false</t>
+          <t>Dispatched to inbox, code verifies successfully</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -941,37 +941,37 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC-EVAL-003</t>
+          <t>TC-STAT-001</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Sandbox</t>
+          <t>Gamification</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Infinite loop terminates at 5s timeout</t>
+          <t>Ensure clean zero-state for newly registered accounts</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Sandbox active</t>
+          <t>Brand new user</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>POST /api/challenges/&lt;pk&gt;/run with while True</t>
+          <t>Navigate to profile / notifications</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Timeout captured gracefully</t>
+          <t>0 streak, 0 XP, 0 solved, empty badges, no phantom stats</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -983,17 +983,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC-EVAL-004</t>
+          <t>TC-EVAL-001</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>SQL Engine</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Verify interactive SQL query execution</t>
+          <t>Execute correct Python code solution</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>SQL challenge</t>
+          <t>Challenge exists</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>POST /api/challenges/SQL-E01/run with query</t>
+          <t>POST /api/challenges/&lt;pk&gt;/run with valid code</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200 + matching rows</t>
+          <t>HTTP 200 + success: true</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1025,37 +1025,37 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC-EVAL-005</t>
+          <t>TC-EVAL-002</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>SQL Security</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Block destructive SQL extensions/attach</t>
+          <t>Execute failing Python code solution</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>SQL runner</t>
+          <t>Challenge exists</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Evaluate SELECT load_extension(...)</t>
+          <t>POST /api/challenges/&lt;pk&gt;/run with wrong code</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Blocked with SECURITY_ERROR</t>
+          <t>HTTP 200 + success: false</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1067,17 +1067,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC-EVAL-006</t>
+          <t>TC-EVAL-003</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Sandbox</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Official submission awards XP points</t>
+          <t>Infinite loop terminates at 5s timeout</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Passing code</t>
+          <t>Sandbox active</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>POST /api/challenges/&lt;pk&gt;/submit</t>
+          <t>POST /api/challenges/&lt;pk&gt;/run with while True</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200 + XP awarded</t>
+          <t>Timeout captured gracefully</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1109,37 +1109,37 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC-GAME-001</t>
+          <t>TC-EVAL-004</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Gamification</t>
+          <t>SQL Engine</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Daily streak increments consecutive days</t>
+          <t>Verify interactive SQL query execution</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Solved yesterday</t>
+          <t>SQL challenge</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Record submission today</t>
+          <t>POST /api/challenges/SQL-E01/run with query</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Current streak increments by 1</t>
+          <t>HTTP 200 + matching rows</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1151,37 +1151,37 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC-GAME-002</t>
+          <t>TC-EVAL-005</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Gamification</t>
+          <t>SQL Security</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Daily streak resets on lapse (&gt;1 day)</t>
+          <t>Block destructive SQL extensions/attach</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Solved 3 days ago</t>
+          <t>SQL runner</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Record submission today</t>
+          <t>Evaluate SELECT load_extension(...)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Streak resets to 1</t>
+          <t>Blocked with SECURITY_ERROR</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1193,37 +1193,37 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC-GAME-003</t>
+          <t>TC-EVAL-006</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Gamification</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Leaderboard sorts descending by XP</t>
+          <t>Official submission awards XP points</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Users with XP</t>
+          <t>Passing code</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>GET /api/leaderboard</t>
+          <t>POST /api/challenges/&lt;pk&gt;/submit</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Sorted highest to lowest XP</t>
+          <t>HTTP 200 + XP awarded</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1235,17 +1235,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC-CARE-001</t>
+          <t>TC-GAME-001</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Career Engine</t>
+          <t>Gamification</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Calculate role readiness percentages</t>
+          <t>Daily streak increments consecutive days</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1255,17 +1255,17 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>User profile</t>
+          <t>Solved yesterday</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>GET /api/career-insights</t>
+          <t>Record submission today</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Readiness scores 0-100%</t>
+          <t>Current streak increments by 1</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC-CARE-002</t>
+          <t>TC-GAME-002</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Career Engine</t>
+          <t>Gamification</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Prioritize weakness recommendations</t>
+          <t>Daily streak resets on lapse (&gt;1 day)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Weaknesses set</t>
+          <t>Solved 3 days ago</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>GET /api/challenges/recommendations</t>
+          <t>Record submission today</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Challenges match user weaknesses</t>
+          <t>Streak resets to 1</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1319,17 +1319,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC-ECON-001</t>
+          <t>TC-GAME-003</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>Gamification</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Credit BugBytes upon package checkout</t>
+          <t>Leaderboard sorts descending by XP</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Store packages</t>
+          <t>Users with XP</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>POST /api/store/confirm-payment</t>
+          <t>GET /api/leaderboard</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>BugBytes balance increases</t>
+          <t>Sorted highest to lowest XP</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1361,37 +1361,37 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-ECON-002</t>
+          <t>TC-CARE-001</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>Career Engine</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Refund money on on-time challenge solve</t>
+          <t>Calculate role readiness percentages</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Paid challenge</t>
+          <t>User profile</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Submit passing code within time limit</t>
+          <t>GET /api/career-insights</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Real money refunded (INR)</t>
+          <t>Readiness scores 0-100%</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1403,17 +1403,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC-PVP-001</t>
+          <t>TC-CARE-002</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>PvP Battle</t>
+          <t>Career Engine</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Create battle room with room code</t>
+          <t>Prioritize weakness recommendations</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Logged in</t>
+          <t>Weaknesses set</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>POST /api/pvp/create</t>
+          <t>GET /api/challenges/recommendations</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Room created + 6-char room code</t>
+          <t>Challenges match user weaknesses</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1445,17 +1445,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-PVP-002</t>
+          <t>TC-ECON-001</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>PvP Battle</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Join battle room with valid room code</t>
+          <t>Credit BugBytes upon package checkout</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1465,17 +1465,17 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Room waiting</t>
+          <t>Store packages</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>POST /api/pvp/join with room code</t>
+          <t>POST /api/store/confirm-payment</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Status transitions to MATCHED</t>
+          <t>BugBytes balance increases</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1487,37 +1487,37 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC-PVP-003</t>
+          <t>TC-ECON-002</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>PvP Battle</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Synchronize opponent test case progress</t>
+          <t>Refund money on on-time challenge solve</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Match in progress</t>
+          <t>Paid challenge</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>POST progress update + GET status</t>
+          <t>Submit passing code within time limit</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Opponent sees updated test count</t>
+          <t>Real money refunded (INR)</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1529,17 +1529,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-001</t>
+          <t>TC-PVP-001</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>PvP Battle</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Rate limiter throttles rapid bursts</t>
+          <t>Create battle room with room code</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>API endpoint</t>
+          <t>Logged in</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Send burst exceeding window limit</t>
+          <t>POST /api/pvp/create</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>HTTP 429 Too Many Requests</t>
+          <t>Room created + 6-char room code</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1571,40 +1571,208 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>TC-PVP-002</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>PvP Battle</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Join battle room with valid room code</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Room waiting</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/pvp/join with room code</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Status transitions to MATCHED</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TC-PVP-003</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>PvP Battle</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Synchronize opponent test case progress</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Match in progress</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>POST progress update + GET status</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Opponent sees updated test count</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEC-001</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Rate limiter throttles rapid bursts</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>API endpoint</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Send burst exceeding window limit</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 429 Too Many Requests</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>TC-FE-001</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Vite production bundle compilation</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Source valid</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Run npm run build</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>Exit code 0, dist/ created</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEL-001</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Selenium E2E</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Automated browser testing across 8 user journeys</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Vite + Django active</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Run python testing/selenium_tests.py</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>8 / 8 test cases pass, screenshots saved</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
